--- a/artfynd/A 6067-2023 artfynd.xlsx
+++ b/artfynd/A 6067-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6067-2023 artfynd.xlsx
+++ b/artfynd/A 6067-2023 artfynd.xlsx
@@ -800,11 +800,11 @@
         <v>90632759</v>
       </c>
       <c r="B3" t="n">
-        <v>57508</v>
+        <v>56428</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>324352.8316316069</v>
+        <v>324353</v>
       </c>
       <c r="R3" t="n">
-        <v>6359708.204262014</v>
+        <v>6359708</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>

--- a/artfynd/A 6067-2023 artfynd.xlsx
+++ b/artfynd/A 6067-2023 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>90632759</v>
       </c>
       <c r="B3" t="n">
-        <v>56428</v>
+        <v>56542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 6067-2023 artfynd.xlsx
+++ b/artfynd/A 6067-2023 artfynd.xlsx
@@ -802,11 +802,6 @@
       <c r="B3" t="n">
         <v>56542</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>LC</t>
